--- a/mosip_master/xlsx/doc_type.xlsx
+++ b/mosip_master/xlsx/doc_type.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\Sao-Tome-mosip-master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\eclipse-workspace\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDA98484-98F0-4D23-80AB-A3F4E409B50C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4C8BEFC-F72C-473E-A9F2-352DAC720E95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$1</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="36">
   <si>
     <t>lang_code</t>
   </si>
@@ -51,36 +51,15 @@
     <t>por</t>
   </si>
   <si>
-    <t>Atestado de Residência</t>
-  </si>
-  <si>
-    <t>Conta de energia e água</t>
-  </si>
-  <si>
-    <t>Conta de telecomunicações</t>
-  </si>
-  <si>
-    <t>Assento de Nascimento</t>
-  </si>
-  <si>
     <t>Bilhete de Identidade</t>
   </si>
   <si>
-    <t>Carta de Condução</t>
-  </si>
-  <si>
     <t>Passaporte</t>
   </si>
   <si>
-    <t>Cartão de Eleitor</t>
-  </si>
-  <si>
     <t>Cédula Pessoal</t>
   </si>
   <si>
-    <t>Certidão de Baptismo</t>
-  </si>
-  <si>
     <t>Certidão de casamento</t>
   </si>
   <si>
@@ -93,36 +72,15 @@
     <t>Certificado do Parto</t>
   </si>
   <si>
-    <t>ARE</t>
-  </si>
-  <si>
-    <t>CEA</t>
-  </si>
-  <si>
-    <t>CTL</t>
-  </si>
-  <si>
-    <t>ASN</t>
-  </si>
-  <si>
     <t>BID</t>
   </si>
   <si>
-    <t>CDC</t>
-  </si>
-  <si>
     <t>PAS</t>
   </si>
   <si>
-    <t>CVE</t>
-  </si>
-  <si>
     <t>CED</t>
   </si>
   <si>
-    <t>CBT</t>
-  </si>
-  <si>
     <t>CCM</t>
   </si>
   <si>
@@ -138,45 +96,24 @@
     <t>eng</t>
   </si>
   <si>
-    <t>Proof of Residence</t>
-  </si>
-  <si>
-    <t>Electricity and water bill</t>
-  </si>
-  <si>
-    <t>Telecommunications Bill</t>
-  </si>
-  <si>
     <t>Birth Certificate</t>
   </si>
   <si>
     <t>Identity Card</t>
   </si>
   <si>
-    <t>Driving License</t>
-  </si>
-  <si>
     <t>Passport</t>
   </si>
   <si>
-    <t>Voter Card</t>
-  </si>
-  <si>
     <t>Personal Identity Card</t>
   </si>
   <si>
-    <t>Baptismal Certificate</t>
-  </si>
-  <si>
     <t>Marriage Certificate</t>
   </si>
   <si>
     <t>Vaccination Card</t>
   </si>
   <si>
-    <t>Birth Registration Record</t>
-  </si>
-  <si>
     <t>Health Bulletin</t>
   </si>
   <si>
@@ -190,6 +127,15 @@
   </si>
   <si>
     <t>Certificação de Exceção</t>
+  </si>
+  <si>
+    <t>Declaração de Nascimento</t>
+  </si>
+  <si>
+    <t>DSN</t>
+  </si>
+  <si>
+    <t>Declaration of Birth</t>
   </si>
 </sst>
 </file>
@@ -211,18 +157,12 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -258,7 +198,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -268,7 +208,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -549,7 +488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.453125" customWidth="1"/>
@@ -581,13 +520,13 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>7</v>
+        <v>34</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>5</v>
@@ -595,16 +534,16 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D3" t="s">
-        <v>36</v>
+      <c r="D3" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>5</v>
@@ -615,13 +554,13 @@
         <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>5</v>
@@ -629,16 +568,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>5</v>
@@ -649,13 +588,13 @@
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>5</v>
@@ -663,16 +602,16 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>5</v>
@@ -683,13 +622,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>10</v>
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" t="s">
+        <v>9</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>5</v>
@@ -697,16 +636,16 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>48</v>
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>5</v>
@@ -717,13 +656,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>5</v>
@@ -731,16 +670,16 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" t="s">
-        <v>40</v>
+        <v>17</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>5</v>
@@ -751,13 +690,13 @@
         <v>6</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>5</v>
@@ -765,16 +704,16 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" t="s">
-        <v>41</v>
+        <v>18</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>5</v>
@@ -785,7 +724,7 @@
         <v>6</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C14" t="s">
         <v>13</v>
@@ -799,16 +738,16 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="D15" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>5</v>
@@ -818,14 +757,14 @@
       <c r="A16" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>28</v>
+      <c r="B16" t="s">
+        <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D16" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>5</v>
@@ -833,16 +772,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" t="s">
         <v>28</v>
       </c>
-      <c r="C17" t="s">
-        <v>43</v>
-      </c>
       <c r="D17" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>5</v>
@@ -852,14 +791,14 @@
       <c r="A18" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" t="s">
         <v>29</v>
       </c>
       <c r="C18" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D18" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>5</v>
@@ -867,227 +806,23 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>29</v>
       </c>
       <c r="C19" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="D19" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C20" t="s">
-        <v>16</v>
-      </c>
-      <c r="D20" t="s">
-        <v>16</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>35</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C21" t="s">
-        <v>45</v>
-      </c>
-      <c r="D21" t="s">
-        <v>45</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>6</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C22" t="s">
-        <v>17</v>
-      </c>
-      <c r="D22" t="s">
-        <v>17</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>35</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>6</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>35</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>6</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C26" t="s">
-        <v>20</v>
-      </c>
-      <c r="D26" t="s">
-        <v>20</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>35</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C27" t="s">
-        <v>39</v>
-      </c>
-      <c r="D27" t="s">
-        <v>39</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>6</v>
-      </c>
-      <c r="B28" t="s">
-        <v>34</v>
-      </c>
-      <c r="C28" t="s">
-        <v>19</v>
-      </c>
-      <c r="D28" t="s">
-        <v>19</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>35</v>
-      </c>
-      <c r="B29" t="s">
-        <v>34</v>
-      </c>
-      <c r="C29" t="s">
-        <v>49</v>
-      </c>
-      <c r="D29" t="s">
-        <v>49</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>6</v>
-      </c>
-      <c r="B30" t="s">
-        <v>50</v>
-      </c>
-      <c r="C30" t="s">
-        <v>53</v>
-      </c>
-      <c r="D30" t="s">
-        <v>53</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>35</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C31" t="s">
-        <v>51</v>
-      </c>
-      <c r="D31" t="s">
-        <v>52</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E2" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:E1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
